--- a/artfynd/A 42492-2025 artfynd.xlsx
+++ b/artfynd/A 42492-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128957036</v>
       </c>
       <c r="B2" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42492-2025 artfynd.xlsx
+++ b/artfynd/A 42492-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128957036</v>
       </c>
       <c r="B2" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42492-2025 artfynd.xlsx
+++ b/artfynd/A 42492-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128957036</v>
       </c>
       <c r="B2" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42492-2025 artfynd.xlsx
+++ b/artfynd/A 42492-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128957036</v>
+        <v>104915521</v>
       </c>
       <c r="B2" t="n">
-        <v>58097</v>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Avverkningsanmäld skog Gysinge, Stora Gloten, Dlr</t>
+          <t>Glotklacken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535474</v>
+        <v>535069</v>
       </c>
       <c r="R2" t="n">
-        <v>6681445</v>
+        <v>6681557</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,27 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vanligt förekommande i den äldre kontinuitetsskogen</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,15 +771,131 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Susanne Classon</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Susanne Classon</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128957036</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Avverkningsanmäld skog Gysinge, Stora Gloten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>535474</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6681445</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vanligt förekommande i den äldre kontinuitetsskogen</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Peter Dalin</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Peter Dalin</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42492-2025 artfynd.xlsx
+++ b/artfynd/A 42492-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -808,6 +813,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134920593</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -949,6 +959,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134917957</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1057,6 +1072,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104915521</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1173,8 +1193,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128957036</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 42492-2025 artfynd.xlsx
+++ b/artfynd/A 42492-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134920593</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>134917957</v>
       </c>
       <c r="B3" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
